--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N42_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>18.632027805657</v>
       </c>
       <c r="E2" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F2" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>16.27732016653407</v>
       </c>
       <c r="E3" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F3" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>20.43680828849963</v>
       </c>
       <c r="E4" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F4" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>18.34483677464123</v>
       </c>
       <c r="E5" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F5" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>10.03574514234815</v>
       </c>
       <c r="E6" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F6" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>10.73858671439859</v>
       </c>
       <c r="E7" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F7" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.38249392323108</v>
+        <v>10.62164792638586</v>
       </c>
       <c r="D8" t="n">
-        <v>14.93635189083122</v>
+        <v>7.959865770040443</v>
       </c>
       <c r="E8" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F8" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.62046566986841</v>
+        <v>35.38249392323108</v>
       </c>
       <c r="D9" t="n">
-        <v>19.44339127432178</v>
+        <v>14.93635189083122</v>
       </c>
       <c r="E9" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F9" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.9474552286045</v>
+        <v>19.62046566986841</v>
       </c>
       <c r="D10" t="n">
-        <v>24.69085185736785</v>
+        <v>19.44339127432178</v>
       </c>
       <c r="E10" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F10" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.33472527778623</v>
+        <v>24.9474552286045</v>
       </c>
       <c r="D11" t="n">
-        <v>24.46900773797915</v>
+        <v>24.69085185736785</v>
       </c>
       <c r="E11" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F11" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>2.655557563787718</v>
+        <v>24.33472527778623</v>
       </c>
       <c r="D12" t="n">
-        <v>2.560930142380177</v>
+        <v>24.46900773797915</v>
       </c>
       <c r="E12" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F12" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.16860591079142</v>
+        <v>2.655557563787718</v>
       </c>
       <c r="D13" t="n">
-        <v>19.04837341412812</v>
+        <v>2.560930142380177</v>
       </c>
       <c r="E13" t="n">
-        <v>8.712131457897247</v>
+        <v>8.661591468709423</v>
       </c>
       <c r="F13" t="n">
-        <v>6.714381457601757</v>
+        <v>6.767931991124118</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,23 +864,55 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
+        <v>19.16860591079142</v>
+      </c>
+      <c r="D14" t="n">
+        <v>19.04837341412812</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8.661591468709423</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.767931991124118</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W0035F0003T0006Z000C1N42.png</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
         <v>3.442628482260105</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>4.087320098684271</v>
       </c>
-      <c r="E14" t="n">
-        <v>8.712131457897247</v>
-      </c>
-      <c r="F14" t="n">
-        <v>6.714381457601757</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>T6165</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" t="n">
+        <v>8.661591468709423</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.767931991124118</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.84958227967557</v>
+        <v>3.87555712044728</v>
       </c>
       <c r="D2" t="n">
-        <v>18.632027805657</v>
+        <v>3.027704518419262</v>
       </c>
       <c r="E2" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F2" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.64564800616601</v>
+        <v>2.704917801001976</v>
       </c>
       <c r="D3" t="n">
-        <v>16.27732016653407</v>
+        <v>2.645064527061787</v>
       </c>
       <c r="E3" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F3" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.99615255670799</v>
+        <v>3.899374790465049</v>
       </c>
       <c r="D4" t="n">
-        <v>20.43680828849963</v>
+        <v>3.320981346881191</v>
       </c>
       <c r="E4" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F4" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.10066704218629</v>
+        <v>3.103858394355273</v>
       </c>
       <c r="D5" t="n">
-        <v>18.34483677464123</v>
+        <v>2.9810359758792</v>
       </c>
       <c r="E5" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F5" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.09912294462377</v>
+        <v>1.641107478501363</v>
       </c>
       <c r="D6" t="n">
-        <v>10.03574514234815</v>
+        <v>1.630808585631574</v>
       </c>
       <c r="E6" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F6" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.43342962229773</v>
+        <v>3.645432313623381</v>
       </c>
       <c r="D7" t="n">
-        <v>10.73858671439859</v>
+        <v>1.745020341089771</v>
       </c>
       <c r="E7" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F7" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.62164792638586</v>
+        <v>1.726017788037703</v>
       </c>
       <c r="D8" t="n">
-        <v>7.959865770040443</v>
+        <v>1.293478187631572</v>
       </c>
       <c r="E8" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F8" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38249392323108</v>
+        <v>5.749655262525051</v>
       </c>
       <c r="D9" t="n">
-        <v>14.93635189083122</v>
+        <v>2.427157182260074</v>
       </c>
       <c r="E9" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F9" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.62046566986841</v>
+        <v>3.188325671353616</v>
       </c>
       <c r="D10" t="n">
-        <v>19.44339127432178</v>
+        <v>3.159551082077289</v>
       </c>
       <c r="E10" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F10" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.9474552286045</v>
+        <v>4.053961474648232</v>
       </c>
       <c r="D11" t="n">
-        <v>24.69085185736785</v>
+        <v>4.012263426822276</v>
       </c>
       <c r="E11" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F11" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.33472527778623</v>
+        <v>3.954392857640263</v>
       </c>
       <c r="D12" t="n">
-        <v>24.46900773797915</v>
+        <v>3.976213757421612</v>
       </c>
       <c r="E12" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F12" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>2.655557563787718</v>
+        <v>0.4315281041155042</v>
       </c>
       <c r="D13" t="n">
-        <v>2.560930142380177</v>
+        <v>0.4161511481367788</v>
       </c>
       <c r="E13" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F13" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.16860591079142</v>
+        <v>3.114898460503607</v>
       </c>
       <c r="D14" t="n">
-        <v>19.04837341412812</v>
+        <v>3.09536067979582</v>
       </c>
       <c r="E14" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F14" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>3.442628482260105</v>
+        <v>0.559427128367267</v>
       </c>
       <c r="D15" t="n">
-        <v>4.087320098684271</v>
+        <v>0.664189516036194</v>
       </c>
       <c r="E15" t="n">
-        <v>8.661591468709423</v>
+        <v>1.407508613665281</v>
       </c>
       <c r="F15" t="n">
-        <v>6.767931991124118</v>
+        <v>1.099788948557669</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
